--- a/artfynd/A 23674-2026 artfynd.xlsx
+++ b/artfynd/A 23674-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122155017</v>
+        <v>134458848</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Högbodarna, Högbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481305</v>
+        <v>481408</v>
       </c>
       <c r="R2" t="n">
-        <v>6950109</v>
+        <v>6950010</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122155007</v>
+        <v>122155022</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481219</v>
+        <v>481446</v>
       </c>
       <c r="R3" t="n">
-        <v>6950176</v>
+        <v>6950153</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122155022</v>
+        <v>122154624</v>
       </c>
       <c r="B4" t="n">
-        <v>78738</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481446</v>
+        <v>481343</v>
       </c>
       <c r="R4" t="n">
-        <v>6950153</v>
+        <v>6949913</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,12 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,53 +976,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122154627</v>
+        <v>134457900</v>
       </c>
       <c r="B5" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481323</v>
+        <v>481279</v>
       </c>
       <c r="R5" t="n">
-        <v>6949942</v>
+        <v>6950179</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1041,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122155015</v>
+        <v>134458038</v>
       </c>
       <c r="B6" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1094,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Högbodarna, Högbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481337</v>
+        <v>481316</v>
       </c>
       <c r="R6" t="n">
-        <v>6950171</v>
+        <v>6950180</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1148,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,12 +1178,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1188,16 +1193,11 @@
         <v>122155005</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1287,19 +1287,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122155018</v>
+        <v>122155007</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1327,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481440</v>
+        <v>481219</v>
       </c>
       <c r="R8" t="n">
-        <v>6950090</v>
+        <v>6950176</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,37 +1384,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122154626</v>
+        <v>122155008</v>
       </c>
       <c r="B9" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481325</v>
+        <v>481230</v>
       </c>
       <c r="R9" t="n">
-        <v>6949943</v>
+        <v>6950220</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1459,12 +1449,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,6 +1478,3391 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122155017</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>481305</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6950109</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122155018</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>481440</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6950090</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134457803</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>481236</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6950164</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134458008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>481291</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6950179</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134458605</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>481426</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6950101</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134458685</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>481422</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6950061</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134459396</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>481331</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6949946</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134459633</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>481336</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6949912</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134460034</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>481291</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6949854</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122155006</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>481224</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6950169</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122154626</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>481325</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6949943</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122154627</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>481323</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6949942</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134459259</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>481329</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6949946</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>19:49</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19:49</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134458281</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>481408</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6950176</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134459413</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>481338</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6949916</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122154625</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>481334</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6949921</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122155023</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>481465</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6950161</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134458715</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>481412</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6950054</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134458907</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>481393</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6950027</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134460223</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>481237</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6949816</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122154629</v>
+      </c>
+      <c r="B30" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>481433</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6949999</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126025921</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>481093</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6950076</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jan Magnesved</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134459830</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>481318</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6949900</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134458552</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>481415</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6950129</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122154630</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>481436</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6949999</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122155009</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>481224</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6950231</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122155015</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bergsvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>481337</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6950171</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134459435</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>481335</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6949938</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134458390</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>481417</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6950145</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134458446</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>481418</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6950149</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134458796</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>481409</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6950029</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134458843</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Högbodarna, Högbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>481404</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6950025</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Hanna Sivertsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134460059</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ledmyrtjärnen, Ledmyrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>481242</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6949848</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23674-2026 artfynd.xlsx
+++ b/artfynd/A 23674-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458848</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154624</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457900</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458038</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155005</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155017</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134457803</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458008</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458605</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458685</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134459396</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134459633</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134460034</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155006</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2605,6 +2700,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154626</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154627</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134459259</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458281</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3023,6 +3138,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134459413</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154625</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3217,6 +3342,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155023</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3319,6 +3449,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458715</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3421,6 +3556,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458907</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3533,6 +3673,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134460223</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3630,6 +3775,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154629</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3735,6 +3885,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126025921</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3837,6 +3992,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134459830</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3949,6 +4109,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458552</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4046,6 +4211,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122154630</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4143,6 +4313,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155009</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4240,6 +4415,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122155015</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4347,6 +4527,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134459435</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4448,6 +4633,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458390</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4554,6 +4744,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458446</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4660,6 +4855,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458796</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4766,6 +4966,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458843</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4863,8 +5068,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134460059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>